--- a/06_Climate_Attribution/00_Index/00_Climate_Data_Index.xlsx
+++ b/06_Climate_Attribution/00_Index/00_Climate_Data_Index.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/53a6410811d0eb69/Downloads/06_Climate_Attribution_Repository_Package_UPDATED/06_Climate_Attribution_Repository_Package_UPDATED/00_Index/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maame\OneDrive\Documents\GitHub\Blue-Mountains-Fire-History-PhD-Supplementary-Repository\06_Climate_Attribution\00_Index\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_A496E5631524886251400048FFB66FC5875FB747" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69F4B224-5EAC-4C4C-82AB-5919C4F217DB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FB68C9-C846-4A38-BCC7-150CECE04AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="15280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="15280" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="File_Index" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="92">
   <si>
     <t>folder</t>
   </si>
@@ -105,12 +105,6 @@
     <t>02a_Southern_Oscillation_Index_Annual_Mean_1866_2025.csv</t>
   </si>
   <si>
-    <t>03_DMI_IPO_Monthly_Index_Cleaned_1950_2026.csv</t>
-  </si>
-  <si>
-    <t>03a_DMI_IPO_Annual_Mean_Index_1950_2026.csv</t>
-  </si>
-  <si>
     <t>04_Climate_Modes_Annual_Combined_1900_2022.csv</t>
   </si>
   <si>
@@ -195,9 +189,6 @@
     <t>CRU/NOAA PSL source retained in uploaded file header</t>
   </si>
   <si>
-    <t>Uploaded DMI_IPO workbook; index identity should be verified before citation</t>
-  </si>
-  <si>
     <t>Derived annual means from climate-mode inputs</t>
   </si>
   <si>
@@ -207,9 +198,6 @@
     <t>Chapters 5-6</t>
   </si>
   <si>
-    <t>Chapter 5</t>
-  </si>
-  <si>
     <t>variable_name</t>
   </si>
   <si>
@@ -294,9 +282,6 @@
     <t>Annual mean Southern Oscillation Index.</t>
   </si>
   <si>
-    <t>Annual mean DMI/IPO index value as provided in the uploaded workbook; verify exact index identity.</t>
-  </si>
-  <si>
     <t>annual_mean_daily_min_vpd_kpa</t>
   </si>
   <si>
@@ -304,6 +289,24 @@
   </si>
   <si>
     <t>days_observed</t>
+  </si>
+  <si>
+    <t>03a_DMI_IOD_Annual_Mean_Index_1950_2026.csv</t>
+  </si>
+  <si>
+    <t>03_DMI_IOD_Monthly_Index_Cleaned_1950_2026.csv</t>
+  </si>
+  <si>
+    <t>Chapters 6</t>
+  </si>
+  <si>
+    <t>Uploaded DMI_IOD workbook; index identity should be verified before citation</t>
+  </si>
+  <si>
+    <t>Annual mean DMI/IOD index value as provided in the uploaded workbook; verify exact index identity.</t>
+  </si>
+  <si>
+    <t>annual_mean_dmi_iod_index</t>
   </si>
 </sst>
 </file>
@@ -313,7 +316,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -325,6 +328,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -728,19 +737,19 @@
         <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -751,19 +760,19 @@
         <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -774,19 +783,19 @@
         <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -797,19 +806,19 @@
         <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -820,19 +829,19 @@
         <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -843,19 +852,19 @@
         <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -866,19 +875,19 @@
         <v>20</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
@@ -889,19 +898,19 @@
         <v>21</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -912,19 +921,19 @@
         <v>22</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -935,19 +944,19 @@
         <v>23</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -955,22 +964,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -978,22 +987,22 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -1001,22 +1010,22 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
@@ -1024,22 +1033,22 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="58" x14ac:dyDescent="0.35">
@@ -1047,22 +1056,22 @@
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="58" x14ac:dyDescent="0.35">
@@ -1070,26 +1079,27 @@
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="F17" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H17" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1104,156 +1114,156 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1275,16 +1285,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -2886,43 +2896,43 @@
   <sheetData>
     <row r="1" spans="1:13" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="J1" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
@@ -6683,25 +6693,25 @@
   <sheetData>
     <row r="1" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
